--- a/mappings/purchases_mapping.xlsx
+++ b/mappings/purchases_mapping.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'PurchaseOrders → purchase.order'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POLines → purchase.order.line'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'PurchaseOrders → purchase.order'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POLines → purchase.order.line'!$A$1:$H$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -498,7 +498,8 @@
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="12.5" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -534,6 +535,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Related Model</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
@@ -569,7 +575,8 @@
           <t>purchase.order</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Primary key preservation. Non-negotiable — needed for reconciliation, dedup, and line linkage.</t>
         </is>
@@ -606,7 +613,8 @@
           <t>purchase.order</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Exact's human-readable PO number. Cannot map to name — Odoo auto-generates name as a sequence (e.g., PO00001). Stored for reference/traceability.</t>
         </is>
@@ -635,7 +643,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.partner</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -644,6 +652,11 @@
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>res.partner</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Vendor account. Lookup: Exact Account GUID → res.partner via x_aa_exact_id. Already mapped in Contacts domain.</t>
         </is>
@@ -672,7 +685,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.partner</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -681,6 +694,11 @@
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>res.partner</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Contact person at supplier. Lookup via x_aa_exact_id on res.partner. No native Odoo PO field for supplier contact — custom field needed.</t>
         </is>
@@ -709,7 +727,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>many2one → account.payment.term</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -718,6 +736,11 @@
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>account.payment.term</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Lookup: Exact PaymentCondition code → account.payment.term via x_aa_code. Already mapped in Contacts domain.</t>
         </is>
@@ -746,7 +769,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.currency</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -755,6 +778,11 @@
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>res.currency</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Lookup by ISO currency code → res.currency.name. Foundational data — assumed pre-existing in Odoo.</t>
         </is>
@@ -783,7 +811,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.partner</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -792,6 +820,11 @@
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>res.partner</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Delivery/drop-ship address. Odoo has native dest_address_id for this. Lookup via x_aa_exact_id on res.partner.</t>
         </is>
@@ -820,7 +853,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.partner</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -829,6 +862,11 @@
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>res.partner</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Contact person at delivery address. No native equivalent — custom field.</t>
         </is>
@@ -857,7 +895,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.users</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -866,6 +904,11 @@
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>res.users</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Buyer/purchase agent. Maps to Odoo's native user_id (Buyer). Lookup: Exact employee/user GUID → res.users. Dependency: requires user mapping (not yet mapped).</t>
         </is>
@@ -894,7 +937,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>many2one → stock.picking.type</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -903,6 +946,11 @@
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>stock.picking.type</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Odoo uses picking_type_id to determine incoming operation type (and hence warehouse). Lookup requires warehouse mapping. Dependency: not yet mapped.</t>
         </is>
@@ -931,7 +979,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>many2one → account.incoterms</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -940,6 +988,11 @@
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>account.incoterms</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Incoterm. Lookup by code → account.incoterms. Odoo has native support.</t>
         </is>
@@ -968,7 +1021,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.users</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -977,6 +1030,11 @@
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>res.users</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Audit field. Lookup user GUID → res.users. Default to admin if unmapped.</t>
         </is>
@@ -1005,7 +1063,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.users</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1014,6 +1072,11 @@
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>res.users</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Audit field. Lookup user GUID → res.users. Default to admin if unmapped.</t>
         </is>
@@ -1042,7 +1105,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.company</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1051,6 +1114,11 @@
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>res.company</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Maps to company. Single-division migration → hardcode to target company.</t>
         </is>
@@ -1087,7 +1155,8 @@
           <t>purchase.order</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Order date. Direct mapping.</t>
         </is>
@@ -1124,7 +1193,8 @@
           <t>purchase.order</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Expected goods receipt date → Odoo's date_planned (Expected Arrival).</t>
         </is>
@@ -1161,7 +1231,8 @@
           <t>purchase.order</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Approval/confirmation datetime. Maps to Odoo's date_approve (Confirmation Date).</t>
         </is>
@@ -1198,7 +1269,8 @@
           <t>purchase.order</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Audit: creation timestamp.</t>
         </is>
@@ -1235,7 +1307,8 @@
           <t>purchase.order</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Audit: last modification timestamp.</t>
         </is>
@@ -1272,7 +1345,8 @@
           <t>purchase.order</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>PO description. Odoo's name is auto-generated sequence — cannot repurpose. No other native description field on purchase.order. Custom field.</t>
         </is>
@@ -1309,7 +1383,8 @@
           <t>purchase.order</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Vendor/supplier reference number. Direct match to Odoo's partner_ref.</t>
         </is>
@@ -1346,7 +1421,8 @@
           <t>purchase.order</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Remarks → Odoo's notes (Terms and Conditions). Type conversion: plain text → HTML.</t>
         </is>
@@ -1383,7 +1459,8 @@
           <t>purchase.order</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Exchange rate. Maps to Odoo's native currency_rate.</t>
         </is>
@@ -1420,7 +1497,8 @@
           <t>purchase.order</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Incoterm location/address. Direct match to Odoo's incoterm_location.</t>
         </is>
@@ -1457,7 +1535,8 @@
           <t>purchase.order</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Drop-ship flag. Odoo handles drop-shipping via routes, not a flag on PO. Custom field for reference.</t>
         </is>
@@ -1494,7 +1573,8 @@
           <t>purchase.order</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>How PO was created (1=Manual, 2=Import, 3=Other, 4=PO, 5=SO, 6=Supplier items, 7=Subcontract, 8=PO advice, 9=Shop order, 10=MRP, 11=REST API, 12=Merge). No Odoo equivalent. Custom field for audit trail.</t>
         </is>
@@ -1531,7 +1611,8 @@
           <t>purchase.order</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Incoterm year version (2010/2020). Odoo doesn't track the version. Custom field.</t>
         </is>
@@ -1568,7 +1649,8 @@
           <t>purchase.order</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Exact status (10=Open, 20=Partial, 30=Complete, 40=Canceled). Stored as-is for reference. State derivation uses this — see Derived rows.</t>
         </is>
@@ -1605,7 +1687,8 @@
           <t>purchase.order</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Receipt status (10=Open, 20=Partial, 30=Complete, 40=Canceled). No single Odoo equivalent — Odoo computes receipt status from stock.picking. Stored for reference.</t>
         </is>
@@ -1642,7 +1725,8 @@
           <t>purchase.order</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Invoice status (10=Open, 20=Partial, 30=Complete, 40=Canceled). Odoo computes invoice_status dynamically from bill lines. Stored for reference.</t>
         </is>
@@ -1679,7 +1763,8 @@
           <t>purchase.order</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Approval status (0=Awaiting, 1=Auto, 2=Approved). Odoo has optional purchase approval workflow but status is embedded in state. Custom field.</t>
         </is>
@@ -1716,7 +1801,8 @@
           <t>purchase.order</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Back-to-back SO reference. Stored as char (GUID) for traceability. Cross-linking to sale.order can be done post-migration if SO domain is mapped.</t>
         </is>
@@ -1753,7 +1839,8 @@
           <t>purchase.order</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Manually linked document GUID. No Odoo equivalent. Stored for reference.</t>
         </is>
@@ -1790,7 +1877,8 @@
           <t>purchase.order</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Selection code (Exact Premium feature). No Odoo equivalent. Stored as char for reference.</t>
         </is>
@@ -1827,7 +1915,8 @@
           <t>purchase.order</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Shipping method. Odoo has delivery carriers (delivery.carrier) but the mapping is not straightforward without a carrier mapping. Store GUID for reference.</t>
         </is>
@@ -1866,6 +1955,11 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
           <t>Total in company currency. Odoo computes amount_total_cc from lines. Skip — computed field.</t>
         </is>
       </c>
@@ -1903,6 +1997,11 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
           <t>Total in transaction currency. Odoo computes amount_total from lines. Skip.</t>
         </is>
       </c>
@@ -1940,6 +2039,11 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
           <t>Untaxed total. Odoo computes amount_untaxed from lines. Skip.</t>
         </is>
       </c>
@@ -1977,6 +2081,11 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
           <t>Discount amount in company currency. Computed from line discounts in Odoo. Skip.</t>
         </is>
       </c>
@@ -2014,6 +2123,11 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
           <t>Discount amount excl VAT. Computed. Skip.</t>
         </is>
       </c>
@@ -2051,6 +2165,11 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
           <t>VAT total. Odoo computes amount_tax from lines. Skip.</t>
         </is>
       </c>
@@ -2088,6 +2207,11 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
           <t>Header-level discount percentage. Actual discounts applied at line level in both Exact and Odoo. Skip.</t>
         </is>
       </c>
@@ -2125,6 +2249,11 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
           <t>Exact stores address as separate GUID. Odoo resolves address from the partner record on dest_address_id. Skip.</t>
         </is>
       </c>
@@ -2162,6 +2291,11 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field for Creator.</t>
         </is>
       </c>
@@ -2199,6 +2333,11 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field for Modifier.</t>
         </is>
       </c>
@@ -2236,6 +2375,11 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field for Approver.</t>
         </is>
       </c>
@@ -2273,6 +2417,11 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
           <t>Approval user. Skip — approval workflow state captured in x_aa_approval_status. Odoo manages its own approval users.</t>
         </is>
       </c>
@@ -2310,6 +2459,11 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field for PurchaseAgent.</t>
         </is>
       </c>
@@ -2347,6 +2501,11 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display copy of supplier code. Derivable from partner_id.</t>
         </is>
       </c>
@@ -2384,6 +2543,11 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display copy of supplier name. Derivable from partner_id.</t>
         </is>
       </c>
@@ -2421,6 +2585,11 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display copy of supplier contact name.</t>
         </is>
       </c>
@@ -2458,6 +2627,11 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display copy of delivery account code.</t>
         </is>
       </c>
@@ -2495,6 +2669,11 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display copy of delivery account name.</t>
         </is>
       </c>
@@ -2532,6 +2711,11 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display copy of delivery contact name.</t>
         </is>
       </c>
@@ -2569,6 +2753,11 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display copy of payment condition.</t>
         </is>
       </c>
@@ -2606,6 +2795,11 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display copy of document subject.</t>
         </is>
       </c>
@@ -2643,6 +2837,11 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display copy of selection code.</t>
         </is>
       </c>
@@ -2680,6 +2879,11 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display copy of selection code description.</t>
         </is>
       </c>
@@ -2717,6 +2921,11 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display copy of shipping method code.</t>
         </is>
       </c>
@@ -2754,6 +2963,11 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display copy of shipping method description.</t>
         </is>
       </c>
@@ -2791,6 +3005,11 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display copy of warehouse code.</t>
         </is>
       </c>
@@ -2828,6 +3047,11 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display copy of warehouse description.</t>
         </is>
       </c>
@@ -2865,6 +3089,11 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
           <t>Computed count. Odoo derives from order_line.</t>
         </is>
       </c>
@@ -2902,6 +3131,11 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
           <t>Embedded collection — mapped separately in PurchaseOrderLines sheet.</t>
         </is>
       </c>
@@ -2939,6 +3173,11 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display copy of linked SO number. GUID stored in x_aa_sales_order_id.</t>
         </is>
       </c>
@@ -2976,6 +3215,11 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display copy of ApprovalStatus.</t>
         </is>
       </c>
@@ -3011,7 +3255,8 @@
           <t>purchase.order</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Derive from OrderStatus: 10(Open)→'purchase', 30(Complete)→'done', 40(Canceled)→'cancel'. Draft POs (if any) may need ApprovalStatus check.</t>
         </is>
@@ -3048,14 +3293,15 @@
           <t>purchase.order</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Auto-generated by Odoo sequence (e.g., PO00001). Let Odoo assign on create. Original Exact number preserved in x_aa_order_number.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3066,7 +3312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -3075,7 +3321,8 @@
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="12.5" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3111,6 +3358,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Related Model</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
@@ -3146,7 +3398,8 @@
           <t>purchase.order.line</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Primary key preservation. Non-negotiable.</t>
         </is>
@@ -3183,7 +3436,8 @@
           <t>purchase.order.line</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Line ordering. Maps to Odoo's sequence for display order.</t>
         </is>
@@ -3212,7 +3466,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>many2one → purchase.order</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -3221,6 +3475,11 @@
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Parent PO link. Lookup: Exact PurchaseOrderID → purchase.order via x_aa_exact_id.</t>
         </is>
@@ -3249,7 +3508,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>many2one → product.product</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3258,6 +3517,11 @@
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>product.product</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Product reference. Lookup: Exact Item GUID → product.product via x_aa_exact_id. Already mapped in Subscriptions/Items domain.</t>
         </is>
@@ -3286,7 +3550,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>many2one → uom.uom</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -3295,6 +3559,11 @@
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>uom.uom</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Unit of measure. Lookup: Exact Unit code → uom.uom via x_aa_code. Already mapped in UoM domain.</t>
         </is>
@@ -3323,7 +3592,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>many2many → account.tax</t>
+          <t>many2many</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -3332,6 +3601,11 @@
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>account.tax</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Tax code. Lookup: Exact VAT code → account.tax. Dependency: tax mapping not yet done.</t>
         </is>
@@ -3368,7 +3642,8 @@
           <t>purchase.order.line</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Cost center → Odoo analytic distribution. Lookup: Exact cost center code → account.analytic.account. Dependency: analytic accounts not yet mapped.</t>
         </is>
@@ -3405,7 +3680,8 @@
           <t>purchase.order.line</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Project → may also feed into analytic distribution or a project reference. Depends on Odoo project module config. Dependency: not yet mapped.</t>
         </is>
@@ -3434,7 +3710,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.users</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -3443,6 +3719,11 @@
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>res.users</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Audit field. Default to admin if unmapped.</t>
         </is>
@@ -3471,7 +3752,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.users</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3480,6 +3761,11 @@
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>res.users</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Audit field. Default to admin if unmapped.</t>
         </is>
@@ -3508,7 +3794,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.company</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3517,6 +3803,11 @@
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>res.company</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Hardcode to target company.</t>
         </is>
@@ -3553,7 +3844,8 @@
           <t>purchase.order.line</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Expected delivery date per line. Direct match.</t>
         </is>
@@ -3590,7 +3882,8 @@
           <t>purchase.order.line</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Audit: creation timestamp.</t>
         </is>
@@ -3627,7 +3920,8 @@
           <t>purchase.order.line</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Audit: last modification timestamp.</t>
         </is>
@@ -3664,7 +3958,8 @@
           <t>purchase.order.line</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Line description. Odoo's name on PO line is the description field (not a sequence). Direct mapping.</t>
         </is>
@@ -3701,7 +3996,8 @@
           <t>purchase.order.line</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Quantity ordered in item units. Direct mapping.</t>
         </is>
@@ -3738,7 +4034,8 @@
           <t>purchase.order.line</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Price per purchase unit. Direct mapping.</t>
         </is>
@@ -3775,7 +4072,8 @@
           <t>purchase.order.line</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Line discount %. Odoo has native discount on PO line. Direct mapping.</t>
         </is>
@@ -3812,7 +4110,8 @@
           <t>purchase.order.line</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Line validity start date. No native Odoo equivalent on PO lines. Custom field.</t>
         </is>
@@ -3849,7 +4148,8 @@
           <t>purchase.order.line</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Line validity end date. No native Odoo equivalent on PO lines. Custom field.</t>
         </is>
@@ -3886,7 +4186,8 @@
           <t>purchase.order.line</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Vendor's own item code for this product. Stored for reference. Can be used to populate product.supplierinfo (vendor pricelists) in a future product enrichment pass.</t>
         </is>
@@ -3923,7 +4224,8 @@
           <t>purchase.order.line</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Re-bill flag (professional service). No native Odoo equivalent. Custom field.</t>
         </is>
@@ -3960,7 +4262,8 @@
           <t>purchase.order.line</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Line-level notes. Odoo PO lines don't have a separate notes field. Custom field.</t>
         </is>
@@ -3997,7 +4300,8 @@
           <t>purchase.order.line</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Cost unit code. May feed analytic distribution. Stored for reference until analytic mapping is complete.</t>
         </is>
@@ -4034,7 +4338,8 @@
           <t>purchase.order.line</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>WBS expense reference (professional service). No Odoo equivalent. Stored as GUID.</t>
         </is>
@@ -4071,7 +4376,8 @@
           <t>purchase.order.line</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Back-to-back SO link at line level. Stored as GUID for reference.</t>
         </is>
@@ -4108,7 +4414,8 @@
           <t>purchase.order.line</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Back-to-back SO line link. Stored as GUID for reference.</t>
         </is>
@@ -4147,6 +4454,11 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
           <t>Line amount in company currency. Odoo computes price_subtotal. Skip.</t>
         </is>
       </c>
@@ -4184,6 +4496,11 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
           <t>Line amount in transaction currency. Odoo computes price_subtotal. Skip.</t>
         </is>
       </c>
@@ -4221,6 +4538,11 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
           <t>Computed: unit price after discount. Odoo computes price_unit_discounted. Skip.</t>
         </is>
       </c>
@@ -4258,6 +4580,11 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
           <t>VAT amount. Odoo computes price_tax from taxes_id. Skip.</t>
         </is>
       </c>
@@ -4295,6 +4622,11 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
           <t>VAT %. Derivable from taxes_id. Skip.</t>
         </is>
       </c>
@@ -4332,6 +4664,11 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
           <t>Odoo computes qty_invoiced from linked account.move.line. Skip.</t>
         </is>
       </c>
@@ -4369,6 +4706,11 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
           <t>Odoo computes qty_received from stock.move. Skip.</t>
         </is>
       </c>
@@ -4406,6 +4748,11 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
           <t>Quantity in purchase-specific units. Odoo handles UoM conversion natively. Skip — product_qty + product_uom is sufficient.</t>
         </is>
       </c>
@@ -4443,6 +4790,11 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
           <t>Current stock level. Odoo computes from quants. Skip.</t>
         </is>
       </c>
@@ -4480,6 +4832,11 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
           <t>Projected stock level. Odoo computes dynamically. Skip.</t>
         </is>
       </c>
@@ -4517,6 +4874,11 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
           <t>Item tracking config — lives on product.template.tracking in Odoo. Not a PO line concern. Skip.</t>
         </is>
       </c>
@@ -4554,6 +4916,11 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
           <t>Serial tracking config — product-level. Not a PO line concern. Skip.</t>
         </is>
       </c>
@@ -4591,6 +4958,11 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
           <t>Whether fractional quantities allowed. Odoo handles via UoM rounding. Skip.</t>
         </is>
       </c>
@@ -4628,6 +5000,11 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
           <t>Item barcode. Lives on product.product.barcode. Not a PO line field. Skip.</t>
         </is>
       </c>
@@ -4665,6 +5042,11 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
           <t>Additional barcode. Product-level data. Skip.</t>
         </is>
       </c>
@@ -4702,6 +5084,11 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
           <t>Internal flag for copying remarks from SupplierItem. Operational setting, not migration data. Skip.</t>
         </is>
       </c>
@@ -4739,6 +5126,11 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
           <t>Premium-only custom field endpoint. Always skip per conventions.</t>
         </is>
       </c>
@@ -4776,6 +5168,11 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field for Creator.</t>
         </is>
       </c>
@@ -4813,6 +5210,11 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field for Modifier.</t>
         </is>
       </c>
@@ -4850,6 +5252,11 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display copy of item code. Derivable from product_id.</t>
         </is>
       </c>
@@ -4887,6 +5294,11 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display copy of item description.</t>
         </is>
       </c>
@@ -4924,6 +5336,11 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display copy of cost center.</t>
         </is>
       </c>
@@ -4961,6 +5378,11 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display copy of cost unit.</t>
         </is>
       </c>
@@ -4998,6 +5420,11 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display copy of unit.</t>
         </is>
       </c>
@@ -5035,6 +5462,11 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display copy of VAT code.</t>
         </is>
       </c>
@@ -5072,6 +5504,11 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display copy of project code.</t>
         </is>
       </c>
@@ -5109,6 +5546,11 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display copy of project description.</t>
         </is>
       </c>
@@ -5146,6 +5588,11 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display copy of expense.</t>
         </is>
       </c>
@@ -5183,6 +5630,11 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display copy of linked SO number. GUID stored in x_aa_sales_order_id.</t>
         </is>
       </c>
@@ -5220,6 +5672,11 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display copy of linked SO line number.</t>
         </is>
       </c>
@@ -5257,6 +5714,11 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
           <t>Obsolete per Exact documentation. Skip.</t>
         </is>
       </c>
@@ -5294,6 +5756,11 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
           <t>Obsolete. Skip.</t>
         </is>
       </c>
@@ -5331,6 +5798,11 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
           <t>Obsolete. Skip.</t>
         </is>
       </c>
@@ -5368,6 +5840,11 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
           <t>Obsolete. Skip.</t>
         </is>
       </c>
@@ -5405,6 +5882,11 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
           <t>Manufacturing sub-collection. Out of scope. Skip.</t>
         </is>
       </c>
@@ -5442,6 +5924,11 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
           <t>Obsolete. Skip.</t>
         </is>
       </c>
@@ -5479,6 +5966,11 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
           <t>Obsolete. Skip.</t>
         </is>
       </c>
@@ -5516,6 +6008,11 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
           <t>Manufacturing sub-collection. Out of scope. Skip.</t>
         </is>
       </c>
@@ -5551,14 +6048,15 @@
           <t>purchase.order.line</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Inherited from parent purchase.order.state via related field. Odoo sets automatically.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/mappings/purchases_mapping.xlsx
+++ b/mappings/purchases_mapping.xlsx
@@ -7,13 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PurchaseOrders → purchase.order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="POLines → purchase.order.line" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PurchaseOrde... → purchas..." sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PurchaseOrde... → purchas...1" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'PurchaseOrders → purchase.order'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POLines → purchase.order.line'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'PurchaseOrde... → purchas...'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PurchaseOrde... → purchas...1'!$A$1:$H$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -489,6 +489,2761 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12.5" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="12.5" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Exact Field</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Exact Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Odoo Field</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Odoo Type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Odoo Model</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Related Model</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Guid</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>x_aa_exact_id</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>char</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Primary key preservation. Non-negotiable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>LineNumber</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Int32</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>sequence</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Line ordering. Maps to Odoo's sequence for display order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>PurchaseOrderID</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Guid</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Relational</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>order_id</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>many2one</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Parent PO link. Lookup: Exact PurchaseOrderID → purchase.order via x_aa_exact_id.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Guid</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Relational</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>product_id</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>many2one</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>product.product</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Product reference. Lookup: Exact Item GUID → product.product via x_aa_exact_id. Already mapped in Subscriptions/Items domain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Edm.String</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Relational</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>product_uom</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>many2one</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>uom.uom</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Unit of measure. Lookup: Exact Unit code → uom.uom via x_aa_code. Already mapped in UoM domain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>VATCode</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Edm.String</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Relational</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>taxes_id</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>many2many</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>account.tax</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Tax code. Lookup: Exact VAT code → account.tax. Dependency: tax mapping not yet done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>CostCenter</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Edm.String</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Relational</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>analytic_distribution</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>json</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Cost center → Odoo analytic distribution. Lookup: Exact cost center code → account.analytic.account. Dependency: analytic accounts not yet mapped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Guid</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Relational</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>analytic_distribution</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>json</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Project → may also feed into analytic distribution or a project reference. Depends on Odoo project module config. Dependency: not yet mapped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Guid</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Relational</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>create_uid</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>many2one</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>res.users</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Audit field. Default to admin if unmapped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Modifier</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Guid</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Relational</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>write_uid</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>many2one</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>res.users</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Audit field. Default to admin if unmapped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Int32</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Relational</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>company_id</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>many2one</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>res.company</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Hardcode to target company.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ReceiptDate</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Edm.DateTime</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>date_planned</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Expected delivery date per line. Direct match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Created</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Edm.DateTime</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>create_date</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Audit: creation timestamp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Edm.DateTime</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>write_date</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Audit: last modification timestamp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Edm.String</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Line description. Odoo's name on PO line is the description field (not a sequence). Direct mapping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Double</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>product_qty</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Quantity ordered in item units. Direct mapping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>UnitPrice</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Double</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>price_unit</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Price per purchase unit. Direct mapping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Discount</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Double</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>discount</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Line discount %. Odoo has native discount on PO line. Direct mapping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Edm.DateTime</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>x_aa_date_from</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Line validity start date. No native Odoo equivalent on PO lines. Custom field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Edm.DateTime</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>x_aa_date_to</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Line validity end date. No native Odoo equivalent on PO lines. Custom field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SupplierItemCode</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Edm.String</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>x_aa_supplier_item_code</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>char</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Vendor's own item code for this product. Stored for reference. Can be used to populate product.supplierinfo (vendor pricelists) in a future product enrichment pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Rebill</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Boolean</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>x_aa_rebill</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Re-bill flag (professional service). No native Odoo equivalent. Custom field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Edm.String</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>x_aa_notes</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Line-level notes. Odoo PO lines don't have a separate notes field. Custom field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>CostUnit</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Edm.String</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>x_aa_cost_unit</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>char</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Cost unit code. May feed analytic distribution. Stored for reference until analytic mapping is complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Guid</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>x_aa_expense_id</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>char</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>WBS expense reference (professional service). No Odoo equivalent. Stored as GUID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>SalesOrder</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Guid</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>x_aa_sales_order_id</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>char</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Back-to-back SO link at line level. Stored as GUID for reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>SalesOrderLine</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Guid</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>x_aa_sales_order_line_id</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>char</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Back-to-back SO line link. Stored as GUID for reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>AmountDC</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Double</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Line amount in company currency. Odoo computes price_subtotal. Skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>AmountFC</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Double</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Line amount in transaction currency. Odoo computes price_subtotal. Skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>NetPrice</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Double</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Computed: unit price after discount. Odoo computes price_unit_discounted. Skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>VATAmount</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Double</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>VAT amount. Odoo computes price_tax from taxes_id. Skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>VATPercentage</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Double</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>VAT %. Derivable from taxes_id. Skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>InvoicedQuantity</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Double</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Odoo computes qty_invoiced from linked account.move.line. Skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>ReceivedQuantity</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Double</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Odoo computes qty_received from stock.move. Skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>QuantityInPurchaseUnits</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Double</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Quantity in purchase-specific units. Odoo handles UoM conversion natively. Skip — product_qty + product_uom is sufficient.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>InStock</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Double</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Current stock level. Odoo computes from quants. Skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>ProjectedStock</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Double</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Projected stock level. Odoo computes dynamically. Skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>IsBatchNumberItem</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Byte</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Item tracking config — lives on product.template.tracking in Odoo. Not a PO line concern. Skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>IsSerialNumberItem</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Byte</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Serial tracking config — product-level. Not a PO line concern. Skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>ItemDivisable</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Boolean</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Whether fractional quantities allowed. Odoo handles via UoM rounding. Skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>ItemBarcode</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Edm.String</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Item barcode. Lives on product.product.barcode. Not a PO line field. Skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>ItemBarcodeAdditional</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Edm.String</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Additional barcode. Product-level data. Skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>SupplierItemCopyRemarks</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Byte</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Internal flag for copying remarks from SupplierItem. Operational setting, not migration data. Skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>CustomField</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Edm.String</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Premium-only custom field endpoint. Always skip per conventions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>CreatorFullName</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Edm.String</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Denormalized display field for Creator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>ModifierFullName</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Edm.String</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Denormalized display field for Modifier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>ItemCode</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Edm.String</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Denormalized display copy of item code. Derivable from product_id.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>ItemDescription</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Edm.String</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Denormalized display copy of item description.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>CostCenterDescription</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Edm.String</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Denormalized display copy of cost center.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>CostUnitDescription</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Edm.String</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Denormalized display copy of cost unit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>UnitDescription</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Edm.String</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Denormalized display copy of unit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>VATDescription</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Edm.String</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Denormalized display copy of VAT code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>ProjectCode</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Edm.String</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Denormalized display copy of project code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>ProjectDescription</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Edm.String</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Denormalized display copy of project description.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>ExpenseDescription</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Edm.String</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Denormalized display copy of expense.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>SalesOrderNumber</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Int32</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Denormalized display copy of linked SO number. GUID stored in x_aa_sales_order_id.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>SalesOrderLineNumber</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Int32</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Denormalized display copy of linked SO line number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>ShopOrder</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Guid</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete per Exact documentation. Skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>ShopOrderNumber</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Int32</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete. Skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>ShopOrderMaterialPlan</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Guid</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete. Skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>ShopOrderMaterialPlanLineNumber</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Int32</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete. Skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>ShopOrderMaterialPlans</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>ShopOrderMaterialPlans</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturing sub-collection. Out of scope. Skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>ShopOrderRoutingStepPlan</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Guid</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete. Skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>ShopOrderRoutingStepPlanLineNumber</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Edm.Int32</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete. Skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>ShopOrderRoutingStepPlans</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>ShopOrderRoutingStepPlans</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturing sub-collection. Out of scope. Skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>selection</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Inherited from parent purchase.order.state via related field. Odoo sets automatically.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3297,2761 +6052,6 @@
       <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Auto-generated by Odoo sequence (e.g., PO00001). Let Odoo assign on create. Original Exact number preserved in x_aa_order_number.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:H1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H67"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12.5" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="12.5" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Exact Field</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Exact Type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Odoo Field</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Odoo Type</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Odoo Model</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Related Model</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Guid</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>x_aa_exact_id</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>char</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Primary key preservation. Non-negotiable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>LineNumber</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Int32</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>sequence</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Line ordering. Maps to Odoo's sequence for display order.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>PurchaseOrderID</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Guid</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Relational</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>order_id</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>many2one</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Parent PO link. Lookup: Exact PurchaseOrderID → purchase.order via x_aa_exact_id.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Guid</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Relational</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>product_id</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>many2one</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>product.product</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Product reference. Lookup: Exact Item GUID → product.product via x_aa_exact_id. Already mapped in Subscriptions/Items domain.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Edm.String</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Relational</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>product_uom</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>many2one</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>uom.uom</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Unit of measure. Lookup: Exact Unit code → uom.uom via x_aa_code. Already mapped in UoM domain.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>VATCode</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Edm.String</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Relational</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>taxes_id</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>many2many</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>account.tax</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Tax code. Lookup: Exact VAT code → account.tax. Dependency: tax mapping not yet done.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CostCenter</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Edm.String</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Relational</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>analytic_distribution</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>json</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Cost center → Odoo analytic distribution. Lookup: Exact cost center code → account.analytic.account. Dependency: analytic accounts not yet mapped.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Guid</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Relational</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>analytic_distribution</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>json</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Project → may also feed into analytic distribution or a project reference. Depends on Odoo project module config. Dependency: not yet mapped.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Creator</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Guid</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Relational</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>create_uid</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>many2one</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>res.users</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Audit field. Default to admin if unmapped.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Modifier</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Guid</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Relational</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>write_uid</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>many2one</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>res.users</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Audit field. Default to admin if unmapped.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Division</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Int32</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Relational</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>company_id</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>many2one</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>res.company</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Hardcode to target company.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>ReceiptDate</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Edm.DateTime</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>date_planned</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>datetime</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Expected delivery date per line. Direct match.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Created</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Edm.DateTime</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>create_date</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>datetime</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Audit: creation timestamp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Modified</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Edm.DateTime</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>write_date</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>datetime</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Audit: last modification timestamp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Edm.String</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Line description. Odoo's name on PO line is the description field (not a sequence). Direct mapping.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Double</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>product_qty</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Quantity ordered in item units. Direct mapping.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>UnitPrice</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Double</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>price_unit</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Price per purchase unit. Direct mapping.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Discount</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Double</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>discount</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Line discount %. Odoo has native discount on PO line. Direct mapping.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>From</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Edm.DateTime</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Custom</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>x_aa_date_from</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>datetime</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Line validity start date. No native Odoo equivalent on PO lines. Custom field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>To</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Edm.DateTime</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Custom</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>x_aa_date_to</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>datetime</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Line validity end date. No native Odoo equivalent on PO lines. Custom field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>SupplierItemCode</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Edm.String</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Custom</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>x_aa_supplier_item_code</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>char</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Vendor's own item code for this product. Stored for reference. Can be used to populate product.supplierinfo (vendor pricelists) in a future product enrichment pass.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Rebill</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Boolean</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Custom</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>x_aa_rebill</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Re-bill flag (professional service). No native Odoo equivalent. Custom field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Edm.String</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Custom</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>x_aa_notes</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Line-level notes. Odoo PO lines don't have a separate notes field. Custom field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CostUnit</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Edm.String</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Custom</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>x_aa_cost_unit</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>char</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Cost unit code. May feed analytic distribution. Stored for reference until analytic mapping is complete.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Guid</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Custom</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>x_aa_expense_id</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>char</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>WBS expense reference (professional service). No Odoo equivalent. Stored as GUID.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>SalesOrder</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Guid</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Custom</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>x_aa_sales_order_id</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>char</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Back-to-back SO link at line level. Stored as GUID for reference.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>SalesOrderLine</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Guid</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Custom</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>x_aa_sales_order_line_id</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>char</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Back-to-back SO line link. Stored as GUID for reference.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>AmountDC</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Double</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Line amount in company currency. Odoo computes price_subtotal. Skip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>AmountFC</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Double</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Line amount in transaction currency. Odoo computes price_subtotal. Skip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>NetPrice</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Double</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Computed: unit price after discount. Odoo computes price_unit_discounted. Skip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>VATAmount</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Double</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>VAT amount. Odoo computes price_tax from taxes_id. Skip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>VATPercentage</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Double</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>VAT %. Derivable from taxes_id. Skip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>InvoicedQuantity</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Double</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Odoo computes qty_invoiced from linked account.move.line. Skip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>ReceivedQuantity</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Double</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Odoo computes qty_received from stock.move. Skip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>QuantityInPurchaseUnits</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Double</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Quantity in purchase-specific units. Odoo handles UoM conversion natively. Skip — product_qty + product_uom is sufficient.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>InStock</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Double</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Current stock level. Odoo computes from quants. Skip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>ProjectedStock</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Double</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Projected stock level. Odoo computes dynamically. Skip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>IsBatchNumberItem</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Byte</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Item tracking config — lives on product.template.tracking in Odoo. Not a PO line concern. Skip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>IsSerialNumberItem</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Byte</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Serial tracking config — product-level. Not a PO line concern. Skip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>ItemDivisable</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Boolean</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>Whether fractional quantities allowed. Odoo handles via UoM rounding. Skip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>ItemBarcode</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Edm.String</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Item barcode. Lives on product.product.barcode. Not a PO line field. Skip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>ItemBarcodeAdditional</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Edm.String</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Additional barcode. Product-level data. Skip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>SupplierItemCopyRemarks</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Byte</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Internal flag for copying remarks from SupplierItem. Operational setting, not migration data. Skip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CustomField</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Edm.String</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>Premium-only custom field endpoint. Always skip per conventions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CreatorFullName</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Edm.String</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Denormalized display field for Creator.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>ModifierFullName</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Edm.String</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>Denormalized display field for Modifier.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>ItemCode</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Edm.String</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>Denormalized display copy of item code. Derivable from product_id.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>ItemDescription</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Edm.String</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Denormalized display copy of item description.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CostCenterDescription</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Edm.String</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>Denormalized display copy of cost center.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CostUnitDescription</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Edm.String</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>Denormalized display copy of cost unit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>UnitDescription</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Edm.String</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>Denormalized display copy of unit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>VATDescription</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Edm.String</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Denormalized display copy of VAT code.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>ProjectCode</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Edm.String</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>Denormalized display copy of project code.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>ProjectDescription</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Edm.String</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>Denormalized display copy of project description.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>ExpenseDescription</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Edm.String</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>Denormalized display copy of expense.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>SalesOrderNumber</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Int32</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>Denormalized display copy of linked SO number. GUID stored in x_aa_sales_order_id.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>SalesOrderLineNumber</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Int32</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>Denormalized display copy of linked SO line number.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>ShopOrder</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Guid</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete per Exact documentation. Skip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>ShopOrderNumber</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Int32</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete. Skip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>ShopOrderMaterialPlan</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Guid</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete. Skip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>ShopOrderMaterialPlanLineNumber</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Int32</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete. Skip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>ShopOrderMaterialPlans</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>ShopOrderMaterialPlans</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>Manufacturing sub-collection. Out of scope. Skip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>ShopOrderRoutingStepPlan</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Guid</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete. Skip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>ShopOrderRoutingStepPlanLineNumber</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>Edm.Int32</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete. Skip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>ShopOrderRoutingStepPlans</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>ShopOrderRoutingStepPlans</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>Manufacturing sub-collection. Out of scope. Skip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>Derived</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>selection</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>purchase.order.line</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>Inherited from parent purchase.order.state via related field. Odoo sets automatically.</t>
         </is>
       </c>
     </row>
